--- a/src/tests/loader/jmmi_invalid_fuzzy.xlsx
+++ b/src/tests/loader/jmmi_invalid_fuzzy.xlsx
@@ -148,16 +148,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -404,17 +400,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+  <dimension ref="B1:D1"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
